--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -5348,55 +5348,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130159759</v>
+        <v>130159345</v>
       </c>
       <c r="B43" t="n">
-        <v>79632</v>
+        <v>5197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1352</v>
+        <v>105930</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695972</v>
+        <v>696149</v>
       </c>
       <c r="R43" t="n">
-        <v>6635179</v>
+        <v>6635224</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5425,7 +5418,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5435,12 +5428,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5449,44 +5437,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Barrblandskog med aspinslag</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5497,27 +5459,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130159345</v>
+        <v>130159350</v>
       </c>
       <c r="B44" t="n">
-        <v>5197</v>
+        <v>57741</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5526,16 +5488,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696149</v>
+        <v>695828</v>
       </c>
       <c r="R44" t="n">
-        <v>6635224</v>
+        <v>6635235</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5567,7 +5537,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5577,7 +5547,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5608,10 +5578,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130160009</v>
+        <v>130159376</v>
       </c>
       <c r="B45" t="n">
-        <v>79617</v>
+        <v>98831</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,44 +5589,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1349</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695972</v>
+        <v>696090</v>
       </c>
       <c r="R45" t="n">
-        <v>6635179</v>
+        <v>6635240</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5685,7 +5652,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5695,12 +5662,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5713,50 +5675,15 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Barrblandskog med aspinslag</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>2025133</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5767,56 +5694,55 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130159350</v>
+        <v>130160009</v>
       </c>
       <c r="B46" t="n">
-        <v>57741</v>
+        <v>79617</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1349</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695828</v>
+        <v>695972</v>
       </c>
       <c r="R46" t="n">
-        <v>6635235</v>
+        <v>6635179</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5845,7 +5771,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5855,7 +5781,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5864,18 +5795,54 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Barrblandskog med aspinslag</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>2025133</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5997,49 +5964,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130159376</v>
+        <v>130159365</v>
       </c>
       <c r="B48" t="n">
-        <v>98831</v>
+        <v>97702</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696090</v>
+        <v>696134</v>
       </c>
       <c r="R48" t="n">
-        <v>6635240</v>
+        <v>6635233</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6071,7 +6034,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6081,7 +6044,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6090,7 +6053,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6113,45 +6075,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130159365</v>
+        <v>130159375</v>
       </c>
       <c r="B49" t="n">
-        <v>97702</v>
+        <v>98831</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696134</v>
+        <v>696087</v>
       </c>
       <c r="R49" t="n">
-        <v>6635233</v>
+        <v>6635228</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6183,7 +6149,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6193,7 +6159,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6202,6 +6168,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6224,7 +6191,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130159375</v>
+        <v>130144921</v>
       </c>
       <c r="B50" t="n">
         <v>98831</v>
@@ -6257,19 +6224,29 @@
           <t>3</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
         <v>696087</v>
       </c>
       <c r="R50" t="n">
-        <v>6635228</v>
+        <v>6635238</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6298,7 +6275,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6308,7 +6285,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6317,19 +6294,23 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6340,47 +6321,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130144921</v>
+        <v>130160151</v>
       </c>
       <c r="B51" t="n">
-        <v>98831</v>
+        <v>8451</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6389,10 +6369,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696087</v>
+        <v>695990</v>
       </c>
       <c r="R51" t="n">
-        <v>6635238</v>
+        <v>6635164</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6443,12 +6423,33 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris var. sylvestris</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6470,46 +6471,47 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130160151</v>
+        <v>130144922</v>
       </c>
       <c r="B52" t="n">
-        <v>8451</v>
+        <v>98831</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6518,10 +6520,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695990</v>
+        <v>696080</v>
       </c>
       <c r="R52" t="n">
-        <v>6635164</v>
+        <v>6635231</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6572,33 +6574,12 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris var. sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6620,7 +6601,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130144922</v>
+        <v>130144918</v>
       </c>
       <c r="B53" t="n">
         <v>98831</v>
@@ -6650,7 +6631,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6669,10 +6650,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696080</v>
+        <v>696085</v>
       </c>
       <c r="R53" t="n">
-        <v>6635231</v>
+        <v>6635243</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6750,7 +6731,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130144918</v>
+        <v>130144915</v>
       </c>
       <c r="B54" t="n">
         <v>98831</v>
@@ -6780,7 +6761,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6799,10 +6780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696085</v>
+        <v>696055</v>
       </c>
       <c r="R54" t="n">
-        <v>6635243</v>
+        <v>6635219</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6880,7 +6861,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130144915</v>
+        <v>130144933</v>
       </c>
       <c r="B55" t="n">
         <v>98831</v>
@@ -6910,7 +6891,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6929,10 +6910,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696055</v>
+        <v>696093</v>
       </c>
       <c r="R55" t="n">
-        <v>6635219</v>
+        <v>6635214</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7010,7 +6991,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130144933</v>
+        <v>130144919</v>
       </c>
       <c r="B56" t="n">
         <v>98831</v>
@@ -7040,7 +7021,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7059,10 +7040,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696093</v>
+        <v>696089</v>
       </c>
       <c r="R56" t="n">
-        <v>6635214</v>
+        <v>6635247</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7105,6 +7086,11 @@
       <c r="AB56" t="inlineStr">
         <is>
           <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>1+1+11 skott intill varandra.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7140,7 +7126,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130144919</v>
+        <v>130144910</v>
       </c>
       <c r="B57" t="n">
         <v>98831</v>
@@ -7170,7 +7156,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7189,10 +7175,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696089</v>
+        <v>696038</v>
       </c>
       <c r="R57" t="n">
-        <v>6635247</v>
+        <v>6635235</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7235,11 +7221,6 @@
       <c r="AB57" t="inlineStr">
         <is>
           <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>1+1+11 skott intill varandra.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7275,47 +7256,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130144910</v>
+        <v>130176742</v>
       </c>
       <c r="B58" t="n">
-        <v>98831</v>
+        <v>92357</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7324,7 +7296,7 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696038</v>
+        <v>695824</v>
       </c>
       <c r="R58" t="n">
         <v>6635235</v>
@@ -7384,6 +7356,21 @@
       <c r="AI58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7405,38 +7392,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130176742</v>
+        <v>130144924</v>
       </c>
       <c r="B59" t="n">
-        <v>92357</v>
+        <v>98831</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7445,10 +7441,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695824</v>
+        <v>696086</v>
       </c>
       <c r="R59" t="n">
-        <v>6635235</v>
+        <v>6635229</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7505,21 +7501,6 @@
       <c r="AI59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7541,7 +7522,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130144924</v>
+        <v>130144916</v>
       </c>
       <c r="B60" t="n">
         <v>98831</v>
@@ -7571,7 +7552,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7590,10 +7571,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696086</v>
+        <v>696059</v>
       </c>
       <c r="R60" t="n">
-        <v>6635229</v>
+        <v>6635246</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7671,7 +7652,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130144916</v>
+        <v>130144907</v>
       </c>
       <c r="B61" t="n">
         <v>98831</v>
@@ -7701,7 +7682,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7720,10 +7701,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696059</v>
+        <v>695872</v>
       </c>
       <c r="R61" t="n">
-        <v>6635246</v>
+        <v>6635179</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7768,6 +7749,11 @@
           <t>13:40</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Bland kammossa och husmossa.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7779,7 +7765,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog med lövinslag</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7801,7 +7787,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130144907</v>
+        <v>130144917</v>
       </c>
       <c r="B62" t="n">
         <v>98831</v>
@@ -7831,7 +7817,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7850,10 +7836,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>695872</v>
+        <v>696083</v>
       </c>
       <c r="R62" t="n">
-        <v>6635179</v>
+        <v>6635246</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7898,11 +7884,6 @@
           <t>13:40</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Bland kammossa och husmossa.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7914,7 +7895,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granskog med lövinslag</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7936,59 +7917,52 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130144917</v>
+        <v>130159759</v>
       </c>
       <c r="B63" t="n">
-        <v>98831</v>
+        <v>79632</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1352</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696083</v>
+        <v>695972</v>
       </c>
       <c r="R63" t="n">
-        <v>6635246</v>
+        <v>6635179</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8033,18 +8007,44 @@
           <t>13:40</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrblandskog med aspinslag</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -2241,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130144931</v>
+        <v>130122841</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,50 +2252,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696153</v>
+        <v>696054</v>
       </c>
       <c r="R16" t="n">
-        <v>6635219</v>
+        <v>6635214</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2322,65 +2314,29 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2391,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130122841</v>
+        <v>130144931</v>
       </c>
       <c r="B17" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,42 +2358,50 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696054</v>
+        <v>696153</v>
       </c>
       <c r="R17" t="n">
-        <v>6635214</v>
+        <v>6635219</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2464,29 +2428,65 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>130122536</v>
       </c>
       <c r="B6" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130124525</v>
       </c>
       <c r="B9" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>130124558</v>
       </c>
       <c r="B10" t="n">
-        <v>92289</v>
+        <v>92291</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>130144938</v>
       </c>
       <c r="B11" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>130124411</v>
       </c>
       <c r="B12" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130144936</v>
       </c>
       <c r="B13" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>130122659</v>
       </c>
       <c r="B15" t="n">
-        <v>91863</v>
+        <v>91865</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2497,48 +2497,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130124409</v>
+        <v>130144911</v>
       </c>
       <c r="B18" t="n">
-        <v>91603</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695917</v>
+        <v>696061</v>
       </c>
       <c r="R18" t="n">
-        <v>6635221</v>
+        <v>6635211</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,11 +2579,21 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2578,16 +2602,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2598,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130124470</v>
+        <v>130124409</v>
       </c>
       <c r="B19" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,10 +2662,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695960</v>
+        <v>695917</v>
       </c>
       <c r="R19" t="n">
-        <v>6635194</v>
+        <v>6635221</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2699,62 +2728,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130144911</v>
+        <v>130124470</v>
       </c>
       <c r="B20" t="n">
-        <v>98831</v>
+        <v>91605</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696061</v>
+        <v>695960</v>
       </c>
       <c r="R20" t="n">
-        <v>6635211</v>
+        <v>6635194</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2781,21 +2796,11 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2804,21 +2809,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2829,54 +2829,56 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130122654</v>
+        <v>130124934</v>
       </c>
       <c r="B21" t="n">
-        <v>105897</v>
+        <v>79617</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>1349</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696080</v>
+        <v>695982</v>
       </c>
       <c r="R21" t="n">
-        <v>6635231</v>
+        <v>6635173</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2911,14 +2913,25 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2939,56 +2952,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130124934</v>
+        <v>130122654</v>
       </c>
       <c r="B22" t="n">
-        <v>79617</v>
+        <v>105900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1349</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695982</v>
+        <v>696080</v>
       </c>
       <c r="R22" t="n">
-        <v>6635173</v>
+        <v>6635231</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3023,25 +3034,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3065,7 +3065,7 @@
         <v>130144923</v>
       </c>
       <c r="B23" t="n">
-        <v>91863</v>
+        <v>91865</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>130124420</v>
       </c>
       <c r="B24" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>130144904</v>
       </c>
       <c r="B26" t="n">
-        <v>97704</v>
+        <v>97706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>130124615</v>
       </c>
       <c r="B28" t="n">
-        <v>92289</v>
+        <v>92291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>130159355</v>
       </c>
       <c r="B31" t="n">
-        <v>110987</v>
+        <v>110990</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>130159377</v>
       </c>
       <c r="B33" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>130159410</v>
       </c>
       <c r="B34" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>130159348</v>
       </c>
       <c r="B37" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>130159411</v>
       </c>
       <c r="B39" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4987,48 +4987,64 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130159354</v>
+        <v>130144920</v>
       </c>
       <c r="B40" t="n">
-        <v>57900</v>
+        <v>98833</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696040</v>
+        <v>696088</v>
       </c>
       <c r="R40" t="n">
-        <v>6635238</v>
+        <v>6635243</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5057,7 +5073,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5067,7 +5083,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Två skott, den ena med stängel med blomknopp!</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5076,18 +5097,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5098,64 +5125,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130144920</v>
+        <v>130159354</v>
       </c>
       <c r="B41" t="n">
-        <v>98831</v>
+        <v>57900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696088</v>
+        <v>696040</v>
       </c>
       <c r="R41" t="n">
-        <v>6635243</v>
+        <v>6635238</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5184,7 +5195,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5194,12 +5205,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Två skott, den ena med stängel med blomknopp!</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5208,24 +5214,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5239,7 +5239,7 @@
         <v>130159358</v>
       </c>
       <c r="B42" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5459,56 +5459,55 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130159350</v>
+        <v>130160009</v>
       </c>
       <c r="B44" t="n">
-        <v>57741</v>
+        <v>79617</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1349</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695828</v>
+        <v>695972</v>
       </c>
       <c r="R44" t="n">
-        <v>6635235</v>
+        <v>6635179</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5537,7 +5536,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5547,7 +5546,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5556,18 +5560,54 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Barrblandskog med aspinslag</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>2025133</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5578,49 +5618,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130159376</v>
+        <v>130159350</v>
       </c>
       <c r="B45" t="n">
-        <v>98831</v>
+        <v>57741</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696090</v>
+        <v>695828</v>
       </c>
       <c r="R45" t="n">
-        <v>6635240</v>
+        <v>6635235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5652,7 +5696,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5662,7 +5706,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5671,7 +5715,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5694,55 +5737,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130160009</v>
+        <v>130159356</v>
       </c>
       <c r="B46" t="n">
-        <v>79617</v>
+        <v>110990</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1349</v>
+        <v>219711</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695972</v>
+        <v>695878</v>
       </c>
       <c r="R46" t="n">
-        <v>6635179</v>
+        <v>6635163</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5771,7 +5807,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5781,12 +5817,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5795,54 +5826,18 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Barrblandskog med aspinslag</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>2025133</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5853,45 +5848,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130159356</v>
+        <v>130159376</v>
       </c>
       <c r="B47" t="n">
-        <v>110987</v>
+        <v>98833</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695878</v>
+        <v>696090</v>
       </c>
       <c r="R47" t="n">
-        <v>6635163</v>
+        <v>6635240</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5923,7 +5922,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5933,7 +5932,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5942,6 +5941,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>130159365</v>
       </c>
       <c r="B48" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>130159375</v>
       </c>
       <c r="B49" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>130144921</v>
       </c>
       <c r="B50" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>130144922</v>
       </c>
       <c r="B52" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>130144918</v>
       </c>
       <c r="B53" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>130144915</v>
       </c>
       <c r="B54" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>130144933</v>
       </c>
       <c r="B55" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>130144919</v>
       </c>
       <c r="B56" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>130144910</v>
       </c>
       <c r="B57" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>130176742</v>
       </c>
       <c r="B58" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>130144924</v>
       </c>
       <c r="B59" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>130144916</v>
       </c>
       <c r="B60" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>130144907</v>
       </c>
       <c r="B61" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>130144917</v>
       </c>
       <c r="B62" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>130122536</v>
       </c>
       <c r="B6" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130124525</v>
       </c>
       <c r="B9" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>130124558</v>
       </c>
       <c r="B10" t="n">
-        <v>92291</v>
+        <v>92378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130144938</v>
+        <v>130124411</v>
       </c>
       <c r="B11" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,26 +1692,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696151</v>
+        <v>695949</v>
       </c>
       <c r="R11" t="n">
-        <v>6635217</v>
+        <v>6635209</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,70 +1731,29 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Granlåga.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1812,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130124411</v>
+        <v>130144938</v>
       </c>
       <c r="B12" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,19 +1793,26 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695949</v>
+        <v>696151</v>
       </c>
       <c r="R12" t="n">
-        <v>6635209</v>
+        <v>6635217</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,29 +1839,70 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Granlåga.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1916,7 +1916,7 @@
         <v>130144936</v>
       </c>
       <c r="B13" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>130122659</v>
       </c>
       <c r="B15" t="n">
-        <v>91865</v>
+        <v>91952</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2497,62 +2497,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130144911</v>
+        <v>130124409</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>91692</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696061</v>
+        <v>695917</v>
       </c>
       <c r="R18" t="n">
-        <v>6635211</v>
+        <v>6635221</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2579,21 +2565,11 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2602,21 +2578,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2627,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130124409</v>
+        <v>130124470</v>
       </c>
       <c r="B19" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2662,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695917</v>
+        <v>695960</v>
       </c>
       <c r="R19" t="n">
-        <v>6635221</v>
+        <v>6635194</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2728,48 +2699,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130124470</v>
+        <v>130144911</v>
       </c>
       <c r="B20" t="n">
-        <v>91605</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695960</v>
+        <v>696061</v>
       </c>
       <c r="R20" t="n">
-        <v>6635194</v>
+        <v>6635211</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2796,11 +2781,21 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2809,16 +2804,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2829,56 +2829,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130124934</v>
+        <v>130122654</v>
       </c>
       <c r="B21" t="n">
-        <v>79617</v>
+        <v>105987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1349</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695982</v>
+        <v>696080</v>
       </c>
       <c r="R21" t="n">
-        <v>6635173</v>
+        <v>6635231</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2913,25 +2911,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2952,54 +2939,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130122654</v>
+        <v>130124934</v>
       </c>
       <c r="B22" t="n">
-        <v>105900</v>
+        <v>79702</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>1349</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696080</v>
+        <v>695982</v>
       </c>
       <c r="R22" t="n">
-        <v>6635231</v>
+        <v>6635173</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3034,14 +3023,25 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3062,55 +3062,51 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130144923</v>
+        <v>130124937</v>
       </c>
       <c r="B23" t="n">
-        <v>91865</v>
+        <v>79717</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1106</v>
+        <v>1352</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696074</v>
+        <v>695982</v>
       </c>
       <c r="R23" t="n">
-        <v>6635240</v>
+        <v>6635173</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3137,19 +3133,9 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,40 +3148,15 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3209,7 +3170,7 @@
         <v>130124420</v>
       </c>
       <c r="B24" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3307,51 +3268,44 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130124937</v>
+        <v>130144904</v>
       </c>
       <c r="B25" t="n">
-        <v>79632</v>
+        <v>97793</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1352</v>
+        <v>224363</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Jatta</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695982</v>
+        <v>695880</v>
       </c>
       <c r="R25" t="n">
-        <v>6635173</v>
+        <v>6635144</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3378,30 +3332,44 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3412,41 +3380,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130144904</v>
+        <v>130144923</v>
       </c>
       <c r="B26" t="n">
-        <v>97706</v>
+        <v>91952</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>224363</v>
+        <v>1106</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695880</v>
+        <v>696074</v>
       </c>
       <c r="R26" t="n">
-        <v>6635144</v>
+        <v>6635240</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3497,12 +3476,33 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3635,48 +3635,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130124615</v>
+        <v>130144908</v>
       </c>
       <c r="B28" t="n">
-        <v>92291</v>
+        <v>57826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696048</v>
+        <v>695831</v>
       </c>
       <c r="R28" t="n">
-        <v>6635178</v>
+        <v>6635237</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3703,11 +3711,26 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre födosöksspår.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3716,16 +3739,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3736,56 +3764,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130144908</v>
+        <v>130124615</v>
       </c>
       <c r="B29" t="n">
-        <v>57741</v>
+        <v>92378</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1339</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695831</v>
+        <v>696048</v>
       </c>
       <c r="R29" t="n">
-        <v>6635237</v>
+        <v>6635178</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3812,26 +3832,11 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre födosöksspår.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3840,21 +3845,16 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3979,7 +3979,7 @@
         <v>130159355</v>
       </c>
       <c r="B31" t="n">
-        <v>110990</v>
+        <v>111077</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4087,32 +4087,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130159407</v>
+        <v>130159377</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695872</v>
+        <v>696092</v>
       </c>
       <c r="R32" t="n">
-        <v>6635253</v>
+        <v>6635208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4198,32 +4198,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130159377</v>
+        <v>130159407</v>
       </c>
       <c r="B33" t="n">
-        <v>98833</v>
+        <v>5177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696092</v>
+        <v>695872</v>
       </c>
       <c r="R33" t="n">
-        <v>6635208</v>
+        <v>6635253</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4312,7 +4312,7 @@
         <v>130159410</v>
       </c>
       <c r="B34" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>130159348</v>
       </c>
       <c r="B37" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>130159411</v>
       </c>
       <c r="B39" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4987,64 +4987,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130144920</v>
+        <v>130159354</v>
       </c>
       <c r="B40" t="n">
-        <v>98833</v>
+        <v>57985</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696088</v>
+        <v>696040</v>
       </c>
       <c r="R40" t="n">
-        <v>6635243</v>
+        <v>6635238</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5073,7 +5057,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5083,12 +5067,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Två skott, den ena med stängel med blomknopp!</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5097,24 +5076,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5125,48 +5098,64 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130159354</v>
+        <v>130144920</v>
       </c>
       <c r="B41" t="n">
-        <v>57900</v>
+        <v>98920</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696040</v>
+        <v>696088</v>
       </c>
       <c r="R41" t="n">
-        <v>6635238</v>
+        <v>6635243</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5195,7 +5184,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5205,7 +5194,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Två skott, den ena med stängel med blomknopp!</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5214,18 +5208,24 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5239,7 +5239,7 @@
         <v>130159358</v>
       </c>
       <c r="B42" t="n">
-        <v>91652</v>
+        <v>91739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>130160009</v>
       </c>
       <c r="B44" t="n">
-        <v>79617</v>
+        <v>79702</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5618,53 +5618,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130159350</v>
+        <v>130159356</v>
       </c>
       <c r="B45" t="n">
-        <v>57741</v>
+        <v>111077</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>219711</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695828</v>
+        <v>695878</v>
       </c>
       <c r="R45" t="n">
-        <v>6635235</v>
+        <v>6635163</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5696,7 +5688,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5706,7 +5698,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5737,45 +5729,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130159356</v>
+        <v>130159376</v>
       </c>
       <c r="B46" t="n">
-        <v>110990</v>
+        <v>98920</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695878</v>
+        <v>696090</v>
       </c>
       <c r="R46" t="n">
-        <v>6635163</v>
+        <v>6635240</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5807,7 +5803,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5817,7 +5813,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5826,6 +5822,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5848,49 +5845,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130159376</v>
+        <v>130159350</v>
       </c>
       <c r="B47" t="n">
-        <v>98833</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696090</v>
+        <v>695828</v>
       </c>
       <c r="R47" t="n">
-        <v>6635240</v>
+        <v>6635235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5922,7 +5923,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5932,7 +5933,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5941,7 +5942,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>130159365</v>
       </c>
       <c r="B48" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>130159375</v>
       </c>
       <c r="B49" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>130144921</v>
       </c>
       <c r="B50" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6471,10 +6471,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130144922</v>
+        <v>130144918</v>
       </c>
       <c r="B52" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696080</v>
+        <v>696085</v>
       </c>
       <c r="R52" t="n">
-        <v>6635231</v>
+        <v>6635243</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130144918</v>
+        <v>130144922</v>
       </c>
       <c r="B53" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696085</v>
+        <v>696080</v>
       </c>
       <c r="R53" t="n">
-        <v>6635243</v>
+        <v>6635231</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6734,7 +6734,7 @@
         <v>130144915</v>
       </c>
       <c r="B54" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>130144933</v>
       </c>
       <c r="B55" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>130144919</v>
       </c>
       <c r="B56" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>130144910</v>
       </c>
       <c r="B57" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>130176742</v>
       </c>
       <c r="B58" t="n">
-        <v>92359</v>
+        <v>92446</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>130144924</v>
       </c>
       <c r="B59" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>130144916</v>
       </c>
       <c r="B60" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>130144907</v>
       </c>
       <c r="B61" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>130144917</v>
       </c>
       <c r="B62" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>130159759</v>
       </c>
       <c r="B63" t="n">
-        <v>79632</v>
+        <v>79717</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -1663,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130124411</v>
+        <v>130144938</v>
       </c>
       <c r="B11" t="n">
         <v>91692</v>
@@ -1692,19 +1692,26 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>695949</v>
+        <v>696151</v>
       </c>
       <c r="R11" t="n">
-        <v>6635209</v>
+        <v>6635217</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,29 +1738,70 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Granlåga.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1764,7 +1812,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130144938</v>
+        <v>130124411</v>
       </c>
       <c r="B12" t="n">
         <v>91692</v>
@@ -1793,26 +1841,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696151</v>
+        <v>695949</v>
       </c>
       <c r="R12" t="n">
-        <v>6635217</v>
+        <v>6635209</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,70 +1880,29 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Granlåga.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2829,54 +2829,56 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130122654</v>
+        <v>130124934</v>
       </c>
       <c r="B21" t="n">
-        <v>105987</v>
+        <v>79702</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>1349</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696080</v>
+        <v>695982</v>
       </c>
       <c r="R21" t="n">
-        <v>6635231</v>
+        <v>6635173</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2911,14 +2913,25 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2939,56 +2952,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130124934</v>
+        <v>130122654</v>
       </c>
       <c r="B22" t="n">
-        <v>79702</v>
+        <v>105987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1349</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695982</v>
+        <v>696080</v>
       </c>
       <c r="R22" t="n">
-        <v>6635173</v>
+        <v>6635231</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3023,25 +3034,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3062,51 +3062,44 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130124937</v>
+        <v>130144904</v>
       </c>
       <c r="B23" t="n">
-        <v>79717</v>
+        <v>97793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1352</v>
+        <v>224363</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Jatta</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695982</v>
+        <v>695880</v>
       </c>
       <c r="R23" t="n">
-        <v>6635173</v>
+        <v>6635144</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3133,30 +3126,44 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3167,48 +3174,55 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130124420</v>
+        <v>130144923</v>
       </c>
       <c r="B24" t="n">
-        <v>91728</v>
+        <v>91952</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695949</v>
+        <v>696074</v>
       </c>
       <c r="R24" t="n">
-        <v>6635209</v>
+        <v>6635240</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3235,29 +3249,65 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3268,44 +3318,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130144904</v>
+        <v>130124420</v>
       </c>
       <c r="B25" t="n">
-        <v>97793</v>
+        <v>91728</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>224363</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695880</v>
+        <v>695949</v>
       </c>
       <c r="R25" t="n">
-        <v>6635144</v>
+        <v>6635209</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3332,21 +3386,11 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3355,21 +3399,16 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3380,55 +3419,51 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130144923</v>
+        <v>130124937</v>
       </c>
       <c r="B26" t="n">
-        <v>91952</v>
+        <v>79717</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1106</v>
+        <v>1352</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696074</v>
+        <v>695982</v>
       </c>
       <c r="R26" t="n">
-        <v>6635240</v>
+        <v>6635173</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3455,19 +3490,9 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,40 +3505,15 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
-        </is>
-      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3635,56 +3635,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130144908</v>
+        <v>130122955</v>
       </c>
       <c r="B28" t="n">
-        <v>57826</v>
+        <v>8440</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695831</v>
+        <v>696054</v>
       </c>
       <c r="R28" t="n">
-        <v>6635237</v>
+        <v>6635214</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3711,49 +3712,30 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre födosöksspår.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3865,57 +3847,56 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130122955</v>
+        <v>130144908</v>
       </c>
       <c r="B30" t="n">
-        <v>8440</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696054</v>
+        <v>695831</v>
       </c>
       <c r="R30" t="n">
-        <v>6635214</v>
+        <v>6635237</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3942,30 +3923,49 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre födosöksspår.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4087,32 +4087,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130159377</v>
+        <v>130159407</v>
       </c>
       <c r="B32" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696092</v>
+        <v>695872</v>
       </c>
       <c r="R32" t="n">
-        <v>6635208</v>
+        <v>6635253</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4198,10 +4198,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130159407</v>
+        <v>130159410</v>
       </c>
       <c r="B33" t="n">
-        <v>5177</v>
+        <v>101109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4209,21 +4209,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695872</v>
+        <v>695876</v>
       </c>
       <c r="R33" t="n">
-        <v>6635253</v>
+        <v>6635159</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4309,32 +4309,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130159410</v>
+        <v>130159377</v>
       </c>
       <c r="B34" t="n">
-        <v>101109</v>
+        <v>98920</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695876</v>
+        <v>696092</v>
       </c>
       <c r="R34" t="n">
-        <v>6635159</v>
+        <v>6635208</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -6471,7 +6471,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130144918</v>
+        <v>130144922</v>
       </c>
       <c r="B52" t="n">
         <v>98920</v>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696085</v>
+        <v>696080</v>
       </c>
       <c r="R52" t="n">
-        <v>6635243</v>
+        <v>6635231</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130144922</v>
+        <v>130144918</v>
       </c>
       <c r="B53" t="n">
         <v>98920</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696080</v>
+        <v>696085</v>
       </c>
       <c r="R53" t="n">
-        <v>6635231</v>
+        <v>6635243</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -2497,48 +2497,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130124409</v>
+        <v>130144911</v>
       </c>
       <c r="B18" t="n">
-        <v>91692</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695917</v>
+        <v>696061</v>
       </c>
       <c r="R18" t="n">
-        <v>6635221</v>
+        <v>6635211</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,11 +2579,21 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2578,16 +2602,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2598,7 +2627,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130124470</v>
+        <v>130124409</v>
       </c>
       <c r="B19" t="n">
         <v>91692</v>
@@ -2633,10 +2662,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695960</v>
+        <v>695917</v>
       </c>
       <c r="R19" t="n">
-        <v>6635194</v>
+        <v>6635221</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2699,62 +2728,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130144911</v>
+        <v>130124470</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>91692</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696061</v>
+        <v>695960</v>
       </c>
       <c r="R20" t="n">
-        <v>6635211</v>
+        <v>6635194</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2781,21 +2796,11 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2804,21 +2809,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3174,55 +3174,51 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130144923</v>
+        <v>130124937</v>
       </c>
       <c r="B24" t="n">
-        <v>91952</v>
+        <v>79717</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1106</v>
+        <v>1352</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696074</v>
+        <v>695982</v>
       </c>
       <c r="R24" t="n">
-        <v>6635240</v>
+        <v>6635173</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3249,19 +3245,9 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3274,40 +3260,15 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3318,48 +3279,55 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130124420</v>
+        <v>130144923</v>
       </c>
       <c r="B25" t="n">
-        <v>91728</v>
+        <v>91952</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695949</v>
+        <v>696074</v>
       </c>
       <c r="R25" t="n">
-        <v>6635209</v>
+        <v>6635240</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3386,29 +3354,65 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3419,10 +3423,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130124937</v>
+        <v>130124420</v>
       </c>
       <c r="B26" t="n">
-        <v>79717</v>
+        <v>91728</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3430,37 +3434,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1352</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695982</v>
+        <v>695949</v>
       </c>
       <c r="R26" t="n">
-        <v>6635173</v>
+        <v>6635209</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3501,7 +3502,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3635,10 +3635,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130122955</v>
+        <v>130124615</v>
       </c>
       <c r="B28" t="n">
-        <v>8440</v>
+        <v>92378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3646,46 +3646,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696054</v>
+        <v>696048</v>
       </c>
       <c r="R28" t="n">
-        <v>6635214</v>
+        <v>6635178</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3723,7 +3714,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3735,7 +3725,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3746,48 +3736,56 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130124615</v>
+        <v>130144908</v>
       </c>
       <c r="B29" t="n">
-        <v>92378</v>
+        <v>57826</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1339</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696048</v>
+        <v>695831</v>
       </c>
       <c r="R29" t="n">
-        <v>6635178</v>
+        <v>6635237</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3814,11 +3812,26 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre födosöksspår.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3827,16 +3840,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3847,56 +3865,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130144908</v>
+        <v>130122955</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>8440</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695831</v>
+        <v>696054</v>
       </c>
       <c r="R30" t="n">
-        <v>6635237</v>
+        <v>6635214</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3923,49 +3942,30 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre födosöksspår.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4198,32 +4198,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130159410</v>
+        <v>130159377</v>
       </c>
       <c r="B33" t="n">
-        <v>101109</v>
+        <v>98920</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695876</v>
+        <v>696092</v>
       </c>
       <c r="R33" t="n">
-        <v>6635159</v>
+        <v>6635208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4309,32 +4309,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130159377</v>
+        <v>130159410</v>
       </c>
       <c r="B34" t="n">
-        <v>98920</v>
+        <v>101109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696092</v>
+        <v>695876</v>
       </c>
       <c r="R34" t="n">
-        <v>6635208</v>
+        <v>6635159</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5618,45 +5618,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130159356</v>
+        <v>130159350</v>
       </c>
       <c r="B45" t="n">
-        <v>111077</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219711</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695878</v>
+        <v>695828</v>
       </c>
       <c r="R45" t="n">
-        <v>6635163</v>
+        <v>6635235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5688,7 +5696,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5698,7 +5706,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5729,49 +5737,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130159376</v>
+        <v>130159356</v>
       </c>
       <c r="B46" t="n">
-        <v>98920</v>
+        <v>111077</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696090</v>
+        <v>695878</v>
       </c>
       <c r="R46" t="n">
-        <v>6635240</v>
+        <v>6635163</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5803,7 +5807,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5813,7 +5817,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5822,7 +5826,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5845,53 +5848,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130159350</v>
+        <v>130159376</v>
       </c>
       <c r="B47" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695828</v>
+        <v>696090</v>
       </c>
       <c r="R47" t="n">
-        <v>6635235</v>
+        <v>6635240</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5923,7 +5922,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5933,7 +5932,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5942,6 +5941,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -2497,62 +2497,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130144911</v>
+        <v>130124409</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>91692</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696061</v>
+        <v>695917</v>
       </c>
       <c r="R18" t="n">
-        <v>6635211</v>
+        <v>6635221</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2579,21 +2565,11 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2602,21 +2578,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2627,7 +2598,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130124409</v>
+        <v>130124470</v>
       </c>
       <c r="B19" t="n">
         <v>91692</v>
@@ -2662,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695917</v>
+        <v>695960</v>
       </c>
       <c r="R19" t="n">
-        <v>6635221</v>
+        <v>6635194</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2728,48 +2699,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130124470</v>
+        <v>130144911</v>
       </c>
       <c r="B20" t="n">
-        <v>91692</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695960</v>
+        <v>696061</v>
       </c>
       <c r="R20" t="n">
-        <v>6635194</v>
+        <v>6635211</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2796,11 +2781,21 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2809,16 +2804,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2829,56 +2829,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130124934</v>
+        <v>130122654</v>
       </c>
       <c r="B21" t="n">
-        <v>79702</v>
+        <v>105987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1349</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695982</v>
+        <v>696080</v>
       </c>
       <c r="R21" t="n">
-        <v>6635173</v>
+        <v>6635231</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2913,25 +2911,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2952,54 +2939,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130122654</v>
+        <v>130124934</v>
       </c>
       <c r="B22" t="n">
-        <v>105987</v>
+        <v>79702</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>1349</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696080</v>
+        <v>695982</v>
       </c>
       <c r="R22" t="n">
-        <v>6635231</v>
+        <v>6635173</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3034,14 +3023,25 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3062,44 +3062,51 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130144904</v>
+        <v>130124937</v>
       </c>
       <c r="B23" t="n">
-        <v>97793</v>
+        <v>79717</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>224363</v>
+        <v>1352</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Ramalina sinensis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Jatta</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695880</v>
+        <v>695982</v>
       </c>
       <c r="R23" t="n">
-        <v>6635144</v>
+        <v>6635173</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3126,44 +3133,30 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3174,10 +3167,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130124937</v>
+        <v>130124420</v>
       </c>
       <c r="B24" t="n">
-        <v>79717</v>
+        <v>91728</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3185,37 +3178,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1352</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695982</v>
+        <v>695949</v>
       </c>
       <c r="R24" t="n">
-        <v>6635173</v>
+        <v>6635209</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3256,7 +3246,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3268,7 +3257,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3423,48 +3412,44 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130124420</v>
+        <v>130144904</v>
       </c>
       <c r="B26" t="n">
-        <v>91728</v>
+        <v>97793</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>224363</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695949</v>
+        <v>695880</v>
       </c>
       <c r="R26" t="n">
-        <v>6635209</v>
+        <v>6635144</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3491,11 +3476,21 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3504,16 +3499,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3635,10 +3635,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130124615</v>
+        <v>130122955</v>
       </c>
       <c r="B28" t="n">
-        <v>92378</v>
+        <v>8440</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3646,37 +3646,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696048</v>
+        <v>696054</v>
       </c>
       <c r="R28" t="n">
-        <v>6635178</v>
+        <v>6635214</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3714,6 +3723,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3725,7 +3735,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3736,56 +3746,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130144908</v>
+        <v>130124615</v>
       </c>
       <c r="B29" t="n">
-        <v>57826</v>
+        <v>92378</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1339</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695831</v>
+        <v>696048</v>
       </c>
       <c r="R29" t="n">
-        <v>6635237</v>
+        <v>6635178</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3812,26 +3814,11 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre födosöksspår.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3840,21 +3827,16 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3865,57 +3847,56 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130122955</v>
+        <v>130144908</v>
       </c>
       <c r="B30" t="n">
-        <v>8440</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696054</v>
+        <v>695831</v>
       </c>
       <c r="R30" t="n">
-        <v>6635214</v>
+        <v>6635237</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3942,30 +3923,49 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre födosöksspår.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4087,32 +4087,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130159407</v>
+        <v>130159377</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695872</v>
+        <v>696092</v>
       </c>
       <c r="R32" t="n">
-        <v>6635253</v>
+        <v>6635208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4198,32 +4198,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130159377</v>
+        <v>130159407</v>
       </c>
       <c r="B33" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696092</v>
+        <v>695872</v>
       </c>
       <c r="R33" t="n">
-        <v>6635208</v>
+        <v>6635253</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
@@ -5323,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
@@ -5459,55 +5459,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130160009</v>
+        <v>130159350</v>
       </c>
       <c r="B44" t="n">
-        <v>79702</v>
+        <v>57826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1349</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695972</v>
+        <v>695828</v>
       </c>
       <c r="R44" t="n">
-        <v>6635179</v>
+        <v>6635235</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5536,7 +5537,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5546,12 +5547,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5560,54 +5556,18 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Barrblandskog med aspinslag</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>2025133</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5618,53 +5578,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130159350</v>
+        <v>130159356</v>
       </c>
       <c r="B45" t="n">
-        <v>57826</v>
+        <v>111077</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>219711</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695828</v>
+        <v>695878</v>
       </c>
       <c r="R45" t="n">
-        <v>6635235</v>
+        <v>6635163</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5696,7 +5648,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5706,7 +5658,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5737,48 +5689,55 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130159356</v>
+        <v>130160009</v>
       </c>
       <c r="B46" t="n">
-        <v>111077</v>
+        <v>79702</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219711</v>
+        <v>1349</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695878</v>
+        <v>695972</v>
       </c>
       <c r="R46" t="n">
-        <v>6635163</v>
+        <v>6635179</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5807,7 +5766,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5817,7 +5776,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5826,18 +5790,54 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Barrblandskog med aspinslag</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>2025133</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -4087,32 +4087,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130159377</v>
+        <v>130159407</v>
       </c>
       <c r="B32" t="n">
-        <v>98920</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696092</v>
+        <v>695872</v>
       </c>
       <c r="R32" t="n">
-        <v>6635208</v>
+        <v>6635253</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4198,32 +4198,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130159410</v>
+        <v>130159377</v>
       </c>
       <c r="B33" t="n">
-        <v>101109</v>
+        <v>98920</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695876</v>
+        <v>696092</v>
       </c>
       <c r="R33" t="n">
-        <v>6635159</v>
+        <v>6635208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4309,10 +4309,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130159407</v>
+        <v>130159410</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>101109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,21 +4320,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695872</v>
+        <v>695876</v>
       </c>
       <c r="R34" t="n">
-        <v>6635253</v>
+        <v>6635159</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5459,56 +5459,55 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130159350</v>
+        <v>130160009</v>
       </c>
       <c r="B44" t="n">
-        <v>57826</v>
+        <v>79702</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1349</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695828</v>
+        <v>695972</v>
       </c>
       <c r="R44" t="n">
-        <v>6635235</v>
+        <v>6635179</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5537,7 +5536,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5547,7 +5546,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5556,18 +5560,54 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Barrblandskog med aspinslag</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>2025133</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5578,55 +5618,56 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130160009</v>
+        <v>130159350</v>
       </c>
       <c r="B45" t="n">
-        <v>79702</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1349</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695972</v>
+        <v>695828</v>
       </c>
       <c r="R45" t="n">
-        <v>6635179</v>
+        <v>6635235</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5655,7 +5696,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,12 +5706,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5679,54 +5715,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Barrblandskog med aspinslag</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>2025133</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5737,45 +5737,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130159356</v>
+        <v>130159376</v>
       </c>
       <c r="B46" t="n">
-        <v>111077</v>
+        <v>98920</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695878</v>
+        <v>696090</v>
       </c>
       <c r="R46" t="n">
-        <v>6635163</v>
+        <v>6635240</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5807,7 +5811,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5817,7 +5821,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5826,6 +5830,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5848,49 +5853,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130159376</v>
+        <v>130159356</v>
       </c>
       <c r="B47" t="n">
-        <v>98920</v>
+        <v>111077</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696090</v>
+        <v>695878</v>
       </c>
       <c r="R47" t="n">
-        <v>6635240</v>
+        <v>6635163</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5922,7 +5923,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5932,7 +5933,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5941,7 +5942,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -4087,32 +4087,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130159407</v>
+        <v>130159377</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695872</v>
+        <v>696092</v>
       </c>
       <c r="R32" t="n">
-        <v>6635253</v>
+        <v>6635208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4198,32 +4198,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130159377</v>
+        <v>130159410</v>
       </c>
       <c r="B33" t="n">
-        <v>98920</v>
+        <v>101109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696092</v>
+        <v>695876</v>
       </c>
       <c r="R33" t="n">
-        <v>6635208</v>
+        <v>6635159</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4309,10 +4309,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130159410</v>
+        <v>130159407</v>
       </c>
       <c r="B34" t="n">
-        <v>101109</v>
+        <v>5177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,21 +4320,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695876</v>
+        <v>695872</v>
       </c>
       <c r="R34" t="n">
-        <v>6635159</v>
+        <v>6635253</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4987,64 +4987,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130144920</v>
+        <v>130159354</v>
       </c>
       <c r="B40" t="n">
-        <v>98920</v>
+        <v>57985</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696088</v>
+        <v>696040</v>
       </c>
       <c r="R40" t="n">
-        <v>6635243</v>
+        <v>6635238</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5073,7 +5057,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5083,12 +5067,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Två skott, den ena med stängel med blomknopp!</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5097,24 +5076,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5125,48 +5098,64 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130159354</v>
+        <v>130144920</v>
       </c>
       <c r="B41" t="n">
-        <v>57985</v>
+        <v>98920</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696040</v>
+        <v>696088</v>
       </c>
       <c r="R41" t="n">
-        <v>6635238</v>
+        <v>6635243</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5195,7 +5184,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5205,7 +5194,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Två skott, den ena med stängel med blomknopp!</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5214,18 +5208,24 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5459,55 +5459,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130160009</v>
+        <v>130159350</v>
       </c>
       <c r="B44" t="n">
-        <v>79702</v>
+        <v>57826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1349</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695972</v>
+        <v>695828</v>
       </c>
       <c r="R44" t="n">
-        <v>6635179</v>
+        <v>6635235</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5536,7 +5537,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5546,12 +5547,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5560,54 +5556,18 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Barrblandskog med aspinslag</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>2025133</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5618,56 +5578,55 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130159350</v>
+        <v>130160009</v>
       </c>
       <c r="B45" t="n">
-        <v>57826</v>
+        <v>79702</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1349</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695828</v>
+        <v>695972</v>
       </c>
       <c r="R45" t="n">
-        <v>6635235</v>
+        <v>6635179</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5696,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5706,7 +5665,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5715,18 +5679,54 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Barrblandskog med aspinslag</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>2025133</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5737,49 +5737,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130159376</v>
+        <v>130159356</v>
       </c>
       <c r="B46" t="n">
-        <v>98920</v>
+        <v>111077</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696090</v>
+        <v>695878</v>
       </c>
       <c r="R46" t="n">
-        <v>6635240</v>
+        <v>6635163</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5811,7 +5807,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5821,7 +5817,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5830,7 +5826,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5853,45 +5848,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130159356</v>
+        <v>130159376</v>
       </c>
       <c r="B47" t="n">
-        <v>111077</v>
+        <v>98920</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695878</v>
+        <v>696090</v>
       </c>
       <c r="R47" t="n">
-        <v>6635163</v>
+        <v>6635240</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5923,7 +5922,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5933,7 +5932,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5942,6 +5941,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -3062,52 +3062,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130144923</v>
+        <v>130144904</v>
       </c>
       <c r="B23" t="n">
-        <v>91952</v>
+        <v>97793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1106</v>
+        <v>224363</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696074</v>
+        <v>695880</v>
       </c>
       <c r="R23" t="n">
-        <v>6635240</v>
+        <v>6635144</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3158,33 +3147,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3206,48 +3174,55 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130124420</v>
+        <v>130144923</v>
       </c>
       <c r="B24" t="n">
-        <v>91728</v>
+        <v>91952</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695949</v>
+        <v>696074</v>
       </c>
       <c r="R24" t="n">
-        <v>6635209</v>
+        <v>6635240</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3274,29 +3249,65 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3307,10 +3318,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130124937</v>
+        <v>130124420</v>
       </c>
       <c r="B25" t="n">
-        <v>79717</v>
+        <v>91728</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,37 +3329,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1352</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695982</v>
+        <v>695949</v>
       </c>
       <c r="R25" t="n">
-        <v>6635173</v>
+        <v>6635209</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3387,9 +3395,8 @@
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3401,7 +3408,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3412,44 +3419,51 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130144904</v>
+        <v>130124937</v>
       </c>
       <c r="B26" t="n">
-        <v>97793</v>
+        <v>79717</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>224363</v>
+        <v>1352</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Ramalina sinensis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Jatta</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695880</v>
+        <v>695982</v>
       </c>
       <c r="R26" t="n">
-        <v>6635144</v>
+        <v>6635173</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3476,44 +3490,30 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3635,56 +3635,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130144908</v>
+        <v>130122955</v>
       </c>
       <c r="B28" t="n">
-        <v>57826</v>
+        <v>8440</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695831</v>
+        <v>696054</v>
       </c>
       <c r="R28" t="n">
-        <v>6635237</v>
+        <v>6635214</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3711,49 +3712,30 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre födosöksspår.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3865,10 +3847,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130122955</v>
+        <v>130159355</v>
       </c>
       <c r="B30" t="n">
-        <v>8440</v>
+        <v>111077</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3876,46 +3858,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>219711</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696054</v>
+        <v>695870</v>
       </c>
       <c r="R30" t="n">
-        <v>6635214</v>
+        <v>6635168</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3942,30 +3915,39 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3976,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130159355</v>
+        <v>130159407</v>
       </c>
       <c r="B31" t="n">
-        <v>111077</v>
+        <v>5177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3987,21 +3969,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219711</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4011,10 +3993,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695870</v>
+        <v>695872</v>
       </c>
       <c r="R31" t="n">
-        <v>6635168</v>
+        <v>6635253</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4046,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4309,10 +4291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130159407</v>
+        <v>130159346</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,21 +4302,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4344,10 +4326,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695872</v>
+        <v>695851</v>
       </c>
       <c r="R34" t="n">
-        <v>6635253</v>
+        <v>6635276</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4379,7 +4361,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4389,7 +4371,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4420,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130159346</v>
+        <v>130159408</v>
       </c>
       <c r="B35" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4431,21 +4413,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4455,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695851</v>
+        <v>696107</v>
       </c>
       <c r="R35" t="n">
-        <v>6635276</v>
+        <v>6635221</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4472,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4500,7 +4482,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4509,6 +4491,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4531,10 +4514,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130159408</v>
+        <v>130159348</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>91692</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,21 +4525,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4566,7 +4549,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696107</v>
+        <v>696148</v>
       </c>
       <c r="R36" t="n">
         <v>6635221</v>
@@ -4601,7 +4584,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4611,7 +4594,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4620,7 +4603,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4643,10 +4625,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130159348</v>
+        <v>130159409</v>
       </c>
       <c r="B37" t="n">
-        <v>91692</v>
+        <v>5197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,34 +4636,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696148</v>
+        <v>695857</v>
       </c>
       <c r="R37" t="n">
-        <v>6635221</v>
+        <v>6635269</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4713,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4723,15 +4710,21 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bock gnag</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4754,10 +4747,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130159409</v>
+        <v>130159411</v>
       </c>
       <c r="B38" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4765,39 +4758,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695857</v>
+        <v>696123</v>
       </c>
       <c r="R38" t="n">
-        <v>6635269</v>
+        <v>6635212</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4829,7 +4817,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4839,21 +4827,15 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Bock gnag</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4876,48 +4858,64 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130159411</v>
+        <v>130144920</v>
       </c>
       <c r="B39" t="n">
-        <v>101109</v>
+        <v>98920</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696123</v>
+        <v>696088</v>
       </c>
       <c r="R39" t="n">
-        <v>6635212</v>
+        <v>6635243</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4946,7 +4944,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4956,7 +4954,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Två skott, den ena med stängel med blomknopp!</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4965,18 +4968,24 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -5098,64 +5107,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130144920</v>
+        <v>130159358</v>
       </c>
       <c r="B41" t="n">
-        <v>98920</v>
+        <v>91739</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696088</v>
+        <v>695855</v>
       </c>
       <c r="R41" t="n">
-        <v>6635243</v>
+        <v>6635272</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5184,7 +5177,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5194,38 +5187,28 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Två skott, den ena med stängel med blomknopp!</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5236,10 +5219,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130159358</v>
+        <v>130159345</v>
       </c>
       <c r="B42" t="n">
-        <v>91739</v>
+        <v>5197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5247,21 +5230,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1205</v>
+        <v>105930</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5271,10 +5254,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695855</v>
+        <v>696149</v>
       </c>
       <c r="R42" t="n">
-        <v>6635272</v>
+        <v>6635224</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5306,7 +5289,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5316,16 +5299,15 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5348,48 +5330,55 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130159345</v>
+        <v>130160009</v>
       </c>
       <c r="B43" t="n">
-        <v>5197</v>
+        <v>79702</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>105930</v>
+        <v>1349</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696149</v>
+        <v>695972</v>
       </c>
       <c r="R43" t="n">
-        <v>6635224</v>
+        <v>6635179</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5418,7 +5407,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5428,7 +5417,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5437,18 +5431,54 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Barrblandskog med aspinslag</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>2025133</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5459,53 +5489,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130159350</v>
+        <v>130159356</v>
       </c>
       <c r="B44" t="n">
-        <v>57826</v>
+        <v>111077</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>219711</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695828</v>
+        <v>695878</v>
       </c>
       <c r="R44" t="n">
-        <v>6635235</v>
+        <v>6635163</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5537,7 +5559,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5547,7 +5569,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5578,10 +5600,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130160009</v>
+        <v>130159376</v>
       </c>
       <c r="B45" t="n">
-        <v>79702</v>
+        <v>98920</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5589,44 +5611,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1349</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695972</v>
+        <v>696090</v>
       </c>
       <c r="R45" t="n">
-        <v>6635179</v>
+        <v>6635240</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5655,7 +5674,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,12 +5684,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5683,50 +5697,15 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Barrblandskog med aspinslag</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>2025133</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5737,10 +5716,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130159356</v>
+        <v>130159365</v>
       </c>
       <c r="B46" t="n">
-        <v>111077</v>
+        <v>97791</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5748,16 +5727,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219711</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5772,10 +5751,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695878</v>
+        <v>696134</v>
       </c>
       <c r="R46" t="n">
-        <v>6635163</v>
+        <v>6635233</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5807,7 +5786,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5817,7 +5796,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5848,7 +5827,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130159376</v>
+        <v>130159375</v>
       </c>
       <c r="B47" t="n">
         <v>98920</v>
@@ -5878,7 +5857,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5887,10 +5866,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696090</v>
+        <v>696087</v>
       </c>
       <c r="R47" t="n">
-        <v>6635240</v>
+        <v>6635228</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5922,7 +5901,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5932,7 +5911,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5964,48 +5943,62 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130159365</v>
+        <v>130144921</v>
       </c>
       <c r="B48" t="n">
-        <v>97791</v>
+        <v>98920</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696134</v>
+        <v>696087</v>
       </c>
       <c r="R48" t="n">
-        <v>6635233</v>
+        <v>6635238</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6034,7 +6027,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6044,7 +6037,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6055,16 +6048,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6075,52 +6073,61 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130159375</v>
+        <v>130160151</v>
       </c>
       <c r="B49" t="n">
-        <v>98920</v>
+        <v>8451</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696087</v>
+        <v>695990</v>
       </c>
       <c r="R49" t="n">
-        <v>6635228</v>
+        <v>6635164</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6149,7 +6156,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6159,7 +6166,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6172,15 +6179,40 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6191,7 +6223,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130144921</v>
+        <v>130144922</v>
       </c>
       <c r="B50" t="n">
         <v>98920</v>
@@ -6221,7 +6253,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6240,10 +6272,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696087</v>
+        <v>696080</v>
       </c>
       <c r="R50" t="n">
-        <v>6635238</v>
+        <v>6635231</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6321,46 +6353,47 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130160151</v>
+        <v>130144918</v>
       </c>
       <c r="B51" t="n">
-        <v>8451</v>
+        <v>98920</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6369,10 +6402,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695990</v>
+        <v>696085</v>
       </c>
       <c r="R51" t="n">
-        <v>6635164</v>
+        <v>6635243</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6423,33 +6456,12 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris var. sylvestris</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6471,7 +6483,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130144922</v>
+        <v>130144915</v>
       </c>
       <c r="B52" t="n">
         <v>98920</v>
@@ -6501,7 +6513,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6520,10 +6532,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696080</v>
+        <v>696055</v>
       </c>
       <c r="R52" t="n">
-        <v>6635231</v>
+        <v>6635219</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6601,7 +6613,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130144918</v>
+        <v>130144933</v>
       </c>
       <c r="B53" t="n">
         <v>98920</v>
@@ -6631,7 +6643,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6650,10 +6662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696085</v>
+        <v>696093</v>
       </c>
       <c r="R53" t="n">
-        <v>6635243</v>
+        <v>6635214</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6731,7 +6743,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130144915</v>
+        <v>130144919</v>
       </c>
       <c r="B54" t="n">
         <v>98920</v>
@@ -6761,7 +6773,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6780,10 +6792,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696055</v>
+        <v>696089</v>
       </c>
       <c r="R54" t="n">
-        <v>6635219</v>
+        <v>6635247</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6826,6 +6838,11 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1+1+11 skott intill varandra.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6861,7 +6878,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130144933</v>
+        <v>130144910</v>
       </c>
       <c r="B55" t="n">
         <v>98920</v>
@@ -6891,7 +6908,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6910,10 +6927,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696093</v>
+        <v>696038</v>
       </c>
       <c r="R55" t="n">
-        <v>6635214</v>
+        <v>6635235</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6991,47 +7008,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130144919</v>
+        <v>130176742</v>
       </c>
       <c r="B56" t="n">
-        <v>98920</v>
+        <v>92446</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7040,10 +7048,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696089</v>
+        <v>695824</v>
       </c>
       <c r="R56" t="n">
-        <v>6635247</v>
+        <v>6635235</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7088,11 +7096,6 @@
           <t>13:40</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>1+1+11 skott intill varandra.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7105,6 +7108,21 @@
       <c r="AI56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7126,7 +7144,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130144910</v>
+        <v>130144924</v>
       </c>
       <c r="B57" t="n">
         <v>98920</v>
@@ -7156,7 +7174,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7175,10 +7193,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696038</v>
+        <v>696086</v>
       </c>
       <c r="R57" t="n">
-        <v>6635235</v>
+        <v>6635229</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7256,38 +7274,47 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130176742</v>
+        <v>130144916</v>
       </c>
       <c r="B58" t="n">
-        <v>92446</v>
+        <v>98920</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7296,10 +7323,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>695824</v>
+        <v>696059</v>
       </c>
       <c r="R58" t="n">
-        <v>6635235</v>
+        <v>6635246</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7356,21 +7383,6 @@
       <c r="AI58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7392,7 +7404,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130144924</v>
+        <v>130144907</v>
       </c>
       <c r="B59" t="n">
         <v>98920</v>
@@ -7422,7 +7434,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7441,10 +7453,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696086</v>
+        <v>695872</v>
       </c>
       <c r="R59" t="n">
-        <v>6635229</v>
+        <v>6635179</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7489,6 +7501,11 @@
           <t>13:40</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Bland kammossa och husmossa.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7500,7 +7517,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Granskog med lövinslag</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7522,7 +7539,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130144916</v>
+        <v>130144917</v>
       </c>
       <c r="B60" t="n">
         <v>98920</v>
@@ -7552,7 +7569,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7571,7 +7588,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696059</v>
+        <v>696083</v>
       </c>
       <c r="R60" t="n">
         <v>6635246</v>
@@ -7652,56 +7669,49 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130144907</v>
+        <v>130159759</v>
       </c>
       <c r="B61" t="n">
-        <v>98920</v>
+        <v>79717</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1352</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695872</v>
+        <v>695972</v>
       </c>
       <c r="R61" t="n">
         <v>6635179</v>
@@ -7751,7 +7761,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Bland kammossa och husmossa.</t>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7760,12 +7770,33 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Granskog med lövinslag</t>
+          <t>Barrblandskog med aspinslag</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7787,62 +7818,56 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130144917</v>
+        <v>130159350</v>
       </c>
       <c r="B62" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696083</v>
+        <v>695828</v>
       </c>
       <c r="R62" t="n">
-        <v>6635246</v>
+        <v>6635235</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7871,7 +7896,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7881,7 +7906,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7892,21 +7917,16 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7917,10 +7937,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130159759</v>
+        <v>130144908</v>
       </c>
       <c r="B63" t="n">
-        <v>79717</v>
+        <v>57826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7928,30 +7948,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1352</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7959,10 +7980,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>695972</v>
+        <v>695831</v>
       </c>
       <c r="R63" t="n">
-        <v>6635179</v>
+        <v>6635237</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8009,7 +8030,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
+          <t>Äldre födosöksspår.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8018,33 +8039,12 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Barrblandskog med aspinslag</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>130122536</v>
       </c>
       <c r="B6" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130124525</v>
       </c>
       <c r="B9" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>130124558</v>
       </c>
       <c r="B10" t="n">
-        <v>92378</v>
+        <v>92381</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130124411</v>
+        <v>130144938</v>
       </c>
       <c r="B11" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,19 +1692,26 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>695949</v>
+        <v>696151</v>
       </c>
       <c r="R11" t="n">
-        <v>6635209</v>
+        <v>6635217</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,29 +1738,70 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Granlåga.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1764,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130144938</v>
+        <v>130124411</v>
       </c>
       <c r="B12" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,26 +1841,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696151</v>
+        <v>695949</v>
       </c>
       <c r="R12" t="n">
-        <v>6635217</v>
+        <v>6635209</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,70 +1880,29 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Granlåga.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1916,7 +1916,7 @@
         <v>130144936</v>
       </c>
       <c r="B13" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>130122659</v>
       </c>
       <c r="B15" t="n">
-        <v>91952</v>
+        <v>91955</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130124470</v>
+        <v>130124409</v>
       </c>
       <c r="B18" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695960</v>
+        <v>695917</v>
       </c>
       <c r="R18" t="n">
-        <v>6635194</v>
+        <v>6635221</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2598,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130124409</v>
+        <v>130124470</v>
       </c>
       <c r="B19" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695917</v>
+        <v>695960</v>
       </c>
       <c r="R19" t="n">
-        <v>6635221</v>
+        <v>6635194</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2702,7 +2702,7 @@
         <v>130144911</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,56 +2829,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130124934</v>
+        <v>130122654</v>
       </c>
       <c r="B21" t="n">
-        <v>79702</v>
+        <v>105990</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1349</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695982</v>
+        <v>696080</v>
       </c>
       <c r="R21" t="n">
-        <v>6635173</v>
+        <v>6635231</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2913,25 +2911,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2952,54 +2939,56 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130122654</v>
+        <v>130124934</v>
       </c>
       <c r="B22" t="n">
-        <v>105987</v>
+        <v>79705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>1349</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696080</v>
+        <v>695982</v>
       </c>
       <c r="R22" t="n">
-        <v>6635231</v>
+        <v>6635173</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3034,14 +3023,25 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3065,7 +3065,7 @@
         <v>130144904</v>
       </c>
       <c r="B23" t="n">
-        <v>97793</v>
+        <v>97796</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>130144923</v>
       </c>
       <c r="B24" t="n">
-        <v>91952</v>
+        <v>91955</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>130124420</v>
       </c>
       <c r="B25" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>130124937</v>
       </c>
       <c r="B26" t="n">
-        <v>79717</v>
+        <v>79720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130122955</v>
+        <v>130124615</v>
       </c>
       <c r="B28" t="n">
-        <v>8440</v>
+        <v>92381</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3646,46 +3646,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696054</v>
+        <v>696048</v>
       </c>
       <c r="R28" t="n">
-        <v>6635214</v>
+        <v>6635178</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3723,7 +3714,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3735,7 +3725,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3746,10 +3736,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130124615</v>
+        <v>130122955</v>
       </c>
       <c r="B29" t="n">
-        <v>92378</v>
+        <v>8440</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3757,37 +3747,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696048</v>
+        <v>696054</v>
       </c>
       <c r="R29" t="n">
-        <v>6635178</v>
+        <v>6635214</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3825,6 +3824,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3850,7 +3850,7 @@
         <v>130159355</v>
       </c>
       <c r="B30" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>130159377</v>
       </c>
       <c r="B32" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>130159410</v>
       </c>
       <c r="B33" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>130159348</v>
       </c>
       <c r="B36" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>130159411</v>
       </c>
       <c r="B38" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4858,64 +4858,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130144920</v>
+        <v>130159354</v>
       </c>
       <c r="B39" t="n">
-        <v>98920</v>
+        <v>57985</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696088</v>
+        <v>696040</v>
       </c>
       <c r="R39" t="n">
-        <v>6635243</v>
+        <v>6635238</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4944,7 +4928,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4954,12 +4938,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Två skott, den ena med stängel med blomknopp!</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4968,24 +4947,18 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4996,48 +4969,64 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130159354</v>
+        <v>130144920</v>
       </c>
       <c r="B40" t="n">
-        <v>57985</v>
+        <v>98923</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696040</v>
+        <v>696088</v>
       </c>
       <c r="R40" t="n">
-        <v>6635238</v>
+        <v>6635243</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5066,7 +5055,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5076,7 +5065,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Två skott, den ena med stängel med blomknopp!</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5085,18 +5079,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5110,7 +5110,7 @@
         <v>130159358</v>
       </c>
       <c r="B41" t="n">
-        <v>91739</v>
+        <v>91742</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,55 +5330,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130160009</v>
+        <v>130159356</v>
       </c>
       <c r="B43" t="n">
-        <v>79702</v>
+        <v>111080</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1349</v>
+        <v>219711</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695972</v>
+        <v>695878</v>
       </c>
       <c r="R43" t="n">
-        <v>6635179</v>
+        <v>6635163</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5407,7 +5400,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5417,12 +5410,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5431,54 +5419,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Barrblandskog med aspinslag</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>2025133</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5489,45 +5441,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130159356</v>
+        <v>130159376</v>
       </c>
       <c r="B44" t="n">
-        <v>111077</v>
+        <v>98923</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695878</v>
+        <v>696090</v>
       </c>
       <c r="R44" t="n">
-        <v>6635163</v>
+        <v>6635240</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5559,7 +5515,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5569,7 +5525,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5578,6 +5534,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5600,10 +5557,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130159376</v>
+        <v>130160009</v>
       </c>
       <c r="B45" t="n">
-        <v>98920</v>
+        <v>79705</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,41 +5568,44 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1349</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Fr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696090</v>
+        <v>695972</v>
       </c>
       <c r="R45" t="n">
-        <v>6635240</v>
+        <v>6635179</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5674,7 +5634,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5684,7 +5644,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5697,15 +5662,50 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Barrblandskog med aspinslag</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>2025133</t>
+        </is>
+      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5719,7 +5719,7 @@
         <v>130159365</v>
       </c>
       <c r="B46" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>130159375</v>
       </c>
       <c r="B47" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>130144921</v>
       </c>
       <c r="B48" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>130144922</v>
       </c>
       <c r="B50" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>130144918</v>
       </c>
       <c r="B51" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>130144915</v>
       </c>
       <c r="B52" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>130144933</v>
       </c>
       <c r="B53" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>130144919</v>
       </c>
       <c r="B54" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>130144910</v>
       </c>
       <c r="B55" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>130176742</v>
       </c>
       <c r="B56" t="n">
-        <v>92446</v>
+        <v>92449</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>130144924</v>
       </c>
       <c r="B57" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>130144916</v>
       </c>
       <c r="B58" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>130144907</v>
       </c>
       <c r="B59" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>130144917</v>
       </c>
       <c r="B60" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>130159759</v>
       </c>
       <c r="B61" t="n">
-        <v>79717</v>
+        <v>79720</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>130122536</v>
       </c>
       <c r="B6" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130124525</v>
       </c>
       <c r="B9" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>130124558</v>
       </c>
       <c r="B10" t="n">
-        <v>92381</v>
+        <v>92407</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>130144938</v>
       </c>
       <c r="B11" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>130124411</v>
       </c>
       <c r="B12" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130144936</v>
       </c>
       <c r="B13" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>130122659</v>
       </c>
       <c r="B15" t="n">
-        <v>91955</v>
+        <v>91981</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130144931</v>
+        <v>130122841</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,50 +2252,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696153</v>
+        <v>696054</v>
       </c>
       <c r="R16" t="n">
-        <v>6635219</v>
+        <v>6635214</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2322,65 +2314,29 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2391,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130122841</v>
+        <v>130144931</v>
       </c>
       <c r="B17" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,42 +2358,50 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696054</v>
+        <v>696153</v>
       </c>
       <c r="R17" t="n">
-        <v>6635214</v>
+        <v>6635219</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2464,29 +2428,65 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2500,7 +2500,7 @@
         <v>130124409</v>
       </c>
       <c r="B18" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>130124470</v>
       </c>
       <c r="B19" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>130144911</v>
       </c>
       <c r="B20" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>130122654</v>
       </c>
       <c r="B21" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>130124934</v>
       </c>
       <c r="B22" t="n">
-        <v>79705</v>
+        <v>79731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,41 +3062,52 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130144904</v>
+        <v>130144923</v>
       </c>
       <c r="B23" t="n">
-        <v>97796</v>
+        <v>91981</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>224363</v>
+        <v>1106</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695880</v>
+        <v>696074</v>
       </c>
       <c r="R23" t="n">
-        <v>6635144</v>
+        <v>6635240</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3147,12 +3158,33 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3174,55 +3206,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130144923</v>
+        <v>130124420</v>
       </c>
       <c r="B24" t="n">
-        <v>91955</v>
+        <v>91757</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696074</v>
+        <v>695949</v>
       </c>
       <c r="R24" t="n">
-        <v>6635240</v>
+        <v>6635209</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3249,65 +3274,29 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3318,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130124420</v>
+        <v>130124937</v>
       </c>
       <c r="B25" t="n">
-        <v>91731</v>
+        <v>79746</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3329,34 +3318,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1352</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695949</v>
+        <v>695982</v>
       </c>
       <c r="R25" t="n">
-        <v>6635209</v>
+        <v>6635173</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3395,8 +3387,9 @@
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3408,7 +3401,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3419,51 +3412,44 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130124937</v>
+        <v>130144904</v>
       </c>
       <c r="B26" t="n">
-        <v>79720</v>
+        <v>97822</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1352</v>
+        <v>224363</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Jatta</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695982</v>
+        <v>695880</v>
       </c>
       <c r="R26" t="n">
-        <v>6635173</v>
+        <v>6635144</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3490,30 +3476,44 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3635,10 +3635,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130124615</v>
+        <v>130122955</v>
       </c>
       <c r="B28" t="n">
-        <v>92381</v>
+        <v>8440</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3646,37 +3646,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696048</v>
+        <v>696054</v>
       </c>
       <c r="R28" t="n">
-        <v>6635178</v>
+        <v>6635214</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3714,6 +3723,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3725,7 +3735,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3736,10 +3746,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130122955</v>
+        <v>130124615</v>
       </c>
       <c r="B29" t="n">
-        <v>8440</v>
+        <v>92407</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3747,46 +3757,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696054</v>
+        <v>696048</v>
       </c>
       <c r="R29" t="n">
-        <v>6635214</v>
+        <v>6635178</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3824,7 +3825,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3850,7 +3850,7 @@
         <v>130159355</v>
       </c>
       <c r="B30" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,32 +4069,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130159377</v>
+        <v>130159410</v>
       </c>
       <c r="B32" t="n">
-        <v>98923</v>
+        <v>101138</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696092</v>
+        <v>695876</v>
       </c>
       <c r="R32" t="n">
-        <v>6635208</v>
+        <v>6635159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,32 +4180,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130159410</v>
+        <v>130159377</v>
       </c>
       <c r="B33" t="n">
-        <v>101112</v>
+        <v>98949</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695876</v>
+        <v>696092</v>
       </c>
       <c r="R33" t="n">
-        <v>6635159</v>
+        <v>6635208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4517,7 +4517,7 @@
         <v>130159348</v>
       </c>
       <c r="B36" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>130159411</v>
       </c>
       <c r="B38" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>130159354</v>
       </c>
       <c r="B39" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>130144920</v>
       </c>
       <c r="B40" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>130159358</v>
       </c>
       <c r="B41" t="n">
-        <v>91742</v>
+        <v>91768</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>130159356</v>
       </c>
       <c r="B43" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>130159376</v>
       </c>
       <c r="B44" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>130160009</v>
       </c>
       <c r="B45" t="n">
-        <v>79705</v>
+        <v>79731</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>130159365</v>
       </c>
       <c r="B46" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>130159375</v>
       </c>
       <c r="B47" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>130144921</v>
       </c>
       <c r="B48" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>130144922</v>
       </c>
       <c r="B50" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>130144918</v>
       </c>
       <c r="B51" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6483,10 +6483,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130144915</v>
+        <v>130144933</v>
       </c>
       <c r="B52" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6532,10 +6532,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696055</v>
+        <v>696093</v>
       </c>
       <c r="R52" t="n">
-        <v>6635219</v>
+        <v>6635214</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130144933</v>
+        <v>130144915</v>
       </c>
       <c r="B53" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696093</v>
+        <v>696055</v>
       </c>
       <c r="R53" t="n">
-        <v>6635214</v>
+        <v>6635219</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6746,7 +6746,7 @@
         <v>130144919</v>
       </c>
       <c r="B54" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>130144910</v>
       </c>
       <c r="B55" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>130176742</v>
       </c>
       <c r="B56" t="n">
-        <v>92449</v>
+        <v>92475</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>130144924</v>
       </c>
       <c r="B57" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>130144916</v>
       </c>
       <c r="B58" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>130144907</v>
       </c>
       <c r="B59" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>130144917</v>
       </c>
       <c r="B60" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>130159759</v>
       </c>
       <c r="B61" t="n">
-        <v>79720</v>
+        <v>79746</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>130159350</v>
       </c>
       <c r="B62" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>130144908</v>
       </c>
       <c r="B63" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -1663,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130144938</v>
+        <v>130124411</v>
       </c>
       <c r="B11" t="n">
         <v>91721</v>
@@ -1692,26 +1692,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696151</v>
+        <v>695949</v>
       </c>
       <c r="R11" t="n">
-        <v>6635217</v>
+        <v>6635209</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,70 +1731,29 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Granlåga.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1812,7 +1764,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130124411</v>
+        <v>130144938</v>
       </c>
       <c r="B12" t="n">
         <v>91721</v>
@@ -1841,19 +1793,26 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hummelberget, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695949</v>
+        <v>696151</v>
       </c>
       <c r="R12" t="n">
-        <v>6635209</v>
+        <v>6635217</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,29 +1839,70 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Granlåga.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Kristoffer Stighäll, Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2829,54 +2829,56 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130122654</v>
+        <v>130124934</v>
       </c>
       <c r="B21" t="n">
-        <v>106016</v>
+        <v>79731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>1349</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696080</v>
+        <v>695982</v>
       </c>
       <c r="R21" t="n">
-        <v>6635231</v>
+        <v>6635173</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2911,14 +2913,25 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2939,56 +2952,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130124934</v>
+        <v>130122654</v>
       </c>
       <c r="B22" t="n">
-        <v>79731</v>
+        <v>106016</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1349</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hummelberget, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695982</v>
+        <v>696080</v>
       </c>
       <c r="R22" t="n">
-        <v>6635173</v>
+        <v>6635231</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3023,25 +3034,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Flerskiktad asprik barrblandskog. Kontinuitetsskog.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3958,32 +3958,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130159407</v>
+        <v>130159377</v>
       </c>
       <c r="B31" t="n">
-        <v>5177</v>
+        <v>98949</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695872</v>
+        <v>696092</v>
       </c>
       <c r="R31" t="n">
-        <v>6635253</v>
+        <v>6635208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4069,10 +4069,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130159410</v>
+        <v>130159407</v>
       </c>
       <c r="B32" t="n">
-        <v>101138</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695876</v>
+        <v>695872</v>
       </c>
       <c r="R32" t="n">
-        <v>6635159</v>
+        <v>6635253</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,32 +4180,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130159377</v>
+        <v>130159410</v>
       </c>
       <c r="B33" t="n">
-        <v>98949</v>
+        <v>101138</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696092</v>
+        <v>695876</v>
       </c>
       <c r="R33" t="n">
-        <v>6635208</v>
+        <v>6635159</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -6483,7 +6483,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130144933</v>
+        <v>130144915</v>
       </c>
       <c r="B52" t="n">
         <v>98949</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6532,10 +6532,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696093</v>
+        <v>696055</v>
       </c>
       <c r="R52" t="n">
-        <v>6635214</v>
+        <v>6635219</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6613,7 +6613,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130144915</v>
+        <v>130144933</v>
       </c>
       <c r="B53" t="n">
         <v>98949</v>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696055</v>
+        <v>696093</v>
       </c>
       <c r="R53" t="n">
-        <v>6635219</v>
+        <v>6635214</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>130124558</v>
       </c>
       <c r="B10" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>130124411</v>
       </c>
       <c r="B11" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>130144938</v>
       </c>
       <c r="B12" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130144936</v>
       </c>
       <c r="B13" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>130122659</v>
       </c>
       <c r="B15" t="n">
-        <v>91981</v>
+        <v>91982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>130124409</v>
       </c>
       <c r="B18" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>130124470</v>
       </c>
       <c r="B19" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>130144911</v>
       </c>
       <c r="B20" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>130122654</v>
       </c>
       <c r="B22" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>130144923</v>
       </c>
       <c r="B23" t="n">
-        <v>91981</v>
+        <v>91982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>130124420</v>
       </c>
       <c r="B24" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>130144904</v>
       </c>
       <c r="B26" t="n">
-        <v>97822</v>
+        <v>97823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>130124615</v>
       </c>
       <c r="B29" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>130159355</v>
       </c>
       <c r="B30" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3958,32 +3958,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130159377</v>
+        <v>130159407</v>
       </c>
       <c r="B31" t="n">
-        <v>98949</v>
+        <v>5177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696092</v>
+        <v>695872</v>
       </c>
       <c r="R31" t="n">
-        <v>6635208</v>
+        <v>6635253</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4069,10 +4069,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130159407</v>
+        <v>130159410</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>101139</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695872</v>
+        <v>695876</v>
       </c>
       <c r="R32" t="n">
-        <v>6635253</v>
+        <v>6635159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,32 +4180,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130159410</v>
+        <v>130159377</v>
       </c>
       <c r="B33" t="n">
-        <v>101138</v>
+        <v>98950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695876</v>
+        <v>696092</v>
       </c>
       <c r="R33" t="n">
-        <v>6635159</v>
+        <v>6635208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4517,7 +4517,7 @@
         <v>130159348</v>
       </c>
       <c r="B36" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>130159411</v>
       </c>
       <c r="B38" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>130144920</v>
       </c>
       <c r="B40" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>130159358</v>
       </c>
       <c r="B41" t="n">
-        <v>91768</v>
+        <v>91769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>130159356</v>
       </c>
       <c r="B43" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>130159376</v>
       </c>
       <c r="B44" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>130159365</v>
       </c>
       <c r="B46" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>130159375</v>
       </c>
       <c r="B47" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>130144921</v>
       </c>
       <c r="B48" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>130144922</v>
       </c>
       <c r="B50" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>130144918</v>
       </c>
       <c r="B51" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>130144915</v>
       </c>
       <c r="B52" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>130144933</v>
       </c>
       <c r="B53" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>130144919</v>
       </c>
       <c r="B54" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>130144910</v>
       </c>
       <c r="B55" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>130176742</v>
       </c>
       <c r="B56" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>130144924</v>
       </c>
       <c r="B57" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>130144916</v>
       </c>
       <c r="B58" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>130144907</v>
       </c>
       <c r="B59" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>130144917</v>
       </c>
       <c r="B60" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -3850,7 +3850,7 @@
         <v>130159355</v>
       </c>
       <c r="B30" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3958,32 +3958,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130159407</v>
+        <v>130159377</v>
       </c>
       <c r="B31" t="n">
-        <v>5177</v>
+        <v>98951</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695872</v>
+        <v>696092</v>
       </c>
       <c r="R31" t="n">
-        <v>6635253</v>
+        <v>6635208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4072,7 +4072,7 @@
         <v>130159410</v>
       </c>
       <c r="B32" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4180,32 +4180,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130159377</v>
+        <v>130159407</v>
       </c>
       <c r="B33" t="n">
-        <v>98950</v>
+        <v>5177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696092</v>
+        <v>695872</v>
       </c>
       <c r="R33" t="n">
-        <v>6635208</v>
+        <v>6635253</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4517,7 +4517,7 @@
         <v>130159348</v>
       </c>
       <c r="B36" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>130159411</v>
       </c>
       <c r="B38" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>130144920</v>
       </c>
       <c r="B40" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>130159358</v>
       </c>
       <c r="B41" t="n">
-        <v>91769</v>
+        <v>91770</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,48 +5330,55 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130159356</v>
+        <v>130160009</v>
       </c>
       <c r="B43" t="n">
-        <v>111107</v>
+        <v>79731</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219711</v>
+        <v>1349</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Rännformig brosklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Ramalina calicaris</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hummelberget N om, Upl</t>
+          <t>Hummelberget, N om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695878</v>
+        <v>695972</v>
       </c>
       <c r="R43" t="n">
-        <v>6635163</v>
+        <v>6635179</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5400,7 +5407,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,7 +5417,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5419,18 +5431,54 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Barrblandskog med aspinslag</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>2025133</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5441,49 +5489,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130159376</v>
+        <v>130159356</v>
       </c>
       <c r="B44" t="n">
-        <v>98950</v>
+        <v>111108</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696090</v>
+        <v>695878</v>
       </c>
       <c r="R44" t="n">
-        <v>6635240</v>
+        <v>6635163</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5515,7 +5559,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5525,7 +5569,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5534,7 +5578,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5557,10 +5600,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130160009</v>
+        <v>130159376</v>
       </c>
       <c r="B45" t="n">
-        <v>79731</v>
+        <v>98951</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5568,44 +5611,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1349</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rännformig brosklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramalina calicaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hummelberget, N om, Upl</t>
+          <t>Hummelberget N om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695972</v>
+        <v>696090</v>
       </c>
       <c r="R45" t="n">
-        <v>6635179</v>
+        <v>6635240</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5634,7 +5674,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5644,12 +5684,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>En bit upp på stammen och grenarna på nyfallen grov asp.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5662,50 +5697,15 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Barrblandskog med aspinslag</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # En bit upp på stammen och grenarna på nyfallen grov asp. # Populus tremula</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>2025133</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5719,7 +5719,7 @@
         <v>130159365</v>
       </c>
       <c r="B46" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>130159375</v>
       </c>
       <c r="B47" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>130144921</v>
       </c>
       <c r="B48" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>130144922</v>
       </c>
       <c r="B50" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>130144918</v>
       </c>
       <c r="B51" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>130144915</v>
       </c>
       <c r="B52" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>130144933</v>
       </c>
       <c r="B53" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>130144919</v>
       </c>
       <c r="B54" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>130144910</v>
       </c>
       <c r="B55" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>130176742</v>
       </c>
       <c r="B56" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>130144924</v>
       </c>
       <c r="B57" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>130144916</v>
       </c>
       <c r="B58" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>130144907</v>
       </c>
       <c r="B59" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>130144917</v>
       </c>
       <c r="B60" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -5946,7 +5946,7 @@
         <v>130144921</v>
       </c>
       <c r="B48" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>130144922</v>
       </c>
       <c r="B50" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>130144918</v>
       </c>
       <c r="B51" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>130144915</v>
       </c>
       <c r="B52" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>130144933</v>
       </c>
       <c r="B53" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>130144919</v>
       </c>
       <c r="B54" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>130144910</v>
       </c>
       <c r="B55" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>130176742</v>
       </c>
       <c r="B56" t="n">
-        <v>92477</v>
+        <v>92479</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>130144924</v>
       </c>
       <c r="B57" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>130144916</v>
       </c>
       <c r="B58" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>130144907</v>
       </c>
       <c r="B59" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>130144917</v>
       </c>
       <c r="B60" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>130159759</v>
       </c>
       <c r="B61" t="n">
-        <v>79746</v>
+        <v>79748</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>130159350</v>
       </c>
       <c r="B62" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>130144908</v>
       </c>
       <c r="B63" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -7821,7 +7821,7 @@
         <v>130159350</v>
       </c>
       <c r="B62" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>130144908</v>
       </c>
       <c r="B63" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -7821,7 +7821,7 @@
         <v>130159350</v>
       </c>
       <c r="B62" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>130144908</v>
       </c>
       <c r="B63" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -7821,7 +7821,7 @@
         <v>130159350</v>
       </c>
       <c r="B62" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>130144908</v>
       </c>
       <c r="B63" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 60941-2025 artfynd.xlsx
+++ b/artfynd/A 60941-2025 artfynd.xlsx
@@ -5110,7 +5110,7 @@
         <v>130159358</v>
       </c>
       <c r="B41" t="n">
-        <v>91770</v>
+        <v>91787</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5136,6 +5136,9 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hummelberget N om, Upl</t>
@@ -5194,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
